--- a/rsvp_forms/006_tropical_event_registration--rsvp_forms.xlsx
+++ b/rsvp_forms/006_tropical_event_registration--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-vegetarian'}</t>
+          <t>non-vegetarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Vegetarian'}</t>
+          <t>Non-Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'gluten-free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Gluten-Free'}</t>
+          <t>Gluten-Free</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'event_type_1'}</t>
+          <t>event_type_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Event Type 1'}</t>
+          <t>Event Type 1</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'event_type_2'}</t>
+          <t>event_type_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Event Type 2'}</t>
+          <t>Event Type 2</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'dd/mm/yyyy'}</t>
+          <t>dd/mm/yyyy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'dd/mm/yyyy'}</t>
+          <t>dd/mm/yyyy</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dd-mm-yyyy'}</t>
+          <t>dd-mm-yyyy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'dd-mm-yyyy'}</t>
+          <t>dd-mm-yyyy</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'attendee_1'}</t>
+          <t>attendee_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Attendee 1'}</t>
+          <t>Attendee 1</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'attendee_2'}</t>
+          <t>attendee_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Attendee 2'}</t>
+          <t>Attendee 2</t>
         </is>
       </c>
     </row>
